--- a/web/files/港岛-筲箕湾-傲华.xlsx
+++ b/web/files/港岛-筲箕湾-傲华.xlsx
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -10733,7 +10733,7 @@
           <t>D | 340呎 (1房)
 $805万
 $23,676/呎
-(26年-08月-14日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -10946,7 +10946,7 @@
           <t>D | 340呎 (1房)
 $762万
 $22,418/呎
-(26年-08月-14日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">

--- a/web/files/港岛-筲箕湾-傲华.xlsx
+++ b/web/files/港岛-筲箕湾-傲华.xlsx
@@ -2031,34 +2031,34 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>6972000</v>
+        <v>6693000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>24636</v>
+        <v>23650</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>6623400</v>
+        <v>6693000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>23404</v>
+        <v>23650</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -10831,12 +10831,12 @@
 (25年-11月-21日)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 283呎 (1房)
-$697万
-$24,636/呎
-(在售)</t>
+$669万
+$23,650/呎
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
           <t>D | 340呎 (1房)
 $773万
 $22,729/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -11096,7 +11096,7 @@
           <t>E | 324呎 (1房)
 $778万
 $24,000/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">

--- a/web/files/港岛-筲箕湾-傲华.xlsx
+++ b/web/files/港岛-筲箕湾-傲华.xlsx
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -10836,7 +10836,7 @@
           <t>H | 283呎 (1房)
 $669万
 $23,650/呎
-(26年-09月-16日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-筲箕湾-傲华.xlsx
+++ b/web/files/港岛-筲箕湾-傲华.xlsx
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>4076000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>18443</v>
+        <v>18360</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>4076000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>18443</v>
+        <v>18360</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -11393,9 +11393,9 @@
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
-          <t>G | 221呎 (开放式)
+          <t>G | 222呎 (开放式)
 $408万
-$18,443/呎
+$18,360/呎
 (25年-05月-20日)</t>
         </is>
       </c>
